--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\Model_Demo_Adv_Veda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640561A6-902E-4B94-B3BE-C239BC43ABBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A13E35-B93E-43F2-B527-0564086DECE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAP_BND" sheetId="20" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
   <si>
     <t>~TFM_INS</t>
   </si>
@@ -260,27 +260,6 @@
   </si>
   <si>
     <t>Gas_invalid</t>
-  </si>
-  <si>
-    <t>~TFM_MIG</t>
-  </si>
-  <si>
-    <t>CUM</t>
-  </si>
-  <si>
-    <t>year2</t>
-  </si>
-  <si>
-    <t>BOH-2030</t>
-  </si>
-  <si>
-    <t>*COA*</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>*.5</t>
   </si>
 </sst>
 </file>
@@ -464,7 +443,7 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -476,10 +455,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="29">
     <cellStyle name="60% - Accent2 2" xfId="25" xr:uid="{99FCB2D4-EE99-413B-9642-7E453AE95CE0}"/>
@@ -1204,23 +1182,23 @@
         <f>F16+1</f>
         <v>2011</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16">
         <f t="shared" ref="H16:L16" si="0">G16+1</f>
         <v>2012</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16">
         <f t="shared" si="0"/>
         <v>2013</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16">
         <f t="shared" si="0"/>
         <v>2014</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16">
         <f t="shared" si="0"/>
         <v>2015</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16">
         <f t="shared" si="0"/>
         <v>2016</v>
       </c>
@@ -1235,7 +1213,7 @@
       <c r="D17" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" t="s">
         <v>52</v>
       </c>
       <c r="F17">
@@ -1261,123 +1239,108 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="10" t="s">
+      <c r="B21" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="10" t="s">
+      <c r="B22" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22">
         <v>2005</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22">
         <f>F22+12</f>
         <v>2017</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22">
         <f t="shared" ref="H22" si="1">G22+1</f>
         <v>2018</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22">
         <f t="shared" ref="I22" si="2">H22+1</f>
         <v>2019</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22">
         <f t="shared" ref="J22" si="3">I22+1</f>
         <v>2020</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22">
         <f t="shared" ref="K22" si="4">J22+1</f>
         <v>2021</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22">
         <f t="shared" ref="L22" si="5">K22+1</f>
         <v>2022</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="10" t="s">
+      <c r="B23" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23">
         <v>3</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23">
         <v>3</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23">
         <v>3</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23">
         <v>3</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23">
         <v>3</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23">
         <v>3</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="10" t="s">
+      <c r="B27" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" t="s">
         <v>50</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28">
         <v>2005</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28">
         <f>E28+12</f>
         <v>2017</v>
       </c>
@@ -1386,19 +1349,19 @@
       <c r="A29" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" t="s">
         <v>58</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29">
         <v>999</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29">
         <v>999</v>
       </c>
     </row>
@@ -1409,43 +1372,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001761B2-0FD6-4D51-B74C-BBF5F040EA39}">
-  <dimension ref="B3:E5"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>